--- a/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun29-Jun29.xlsx
+++ b/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun29-Jun29.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,6 +294,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,7 +717,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -842,19 +859,19 @@
         <f>'Daily Breakdown'!J51</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="41">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="42">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="43">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="42">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -862,19 +879,19 @@
         <f>'Daily Breakdown'!K51</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="41">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="42">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="42">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="43">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -924,7 +941,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed below; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -996,7 +1019,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1036,7 +1059,7 @@
       <c r="C5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="44" t="n">
         <v>77.87</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1076,7 +1099,7 @@
       <c r="C6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="44" t="n">
         <v>77.88</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1116,7 +1139,7 @@
       <c r="C7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1156,7 +1179,7 @@
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="44" t="n">
         <v>77.67</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1196,7 +1219,7 @@
       <c r="C9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="44" t="n">
         <v>77.83</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1236,7 +1259,7 @@
       <c r="C10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="44" t="n">
         <v>77.73999999999999</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1276,7 +1299,7 @@
       <c r="C11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="44" t="n">
         <v>77.87</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1316,7 +1339,7 @@
       <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="44" t="n">
         <v>77.72</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1356,7 +1379,7 @@
       <c r="C13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="44" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1396,7 +1419,7 @@
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="44" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1436,7 +1459,7 @@
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1476,7 +1499,7 @@
       <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="44" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1516,7 +1539,7 @@
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="44" t="n">
         <v>77.84</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1556,7 +1579,7 @@
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1596,7 +1619,7 @@
       <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1636,7 +1659,7 @@
       <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1676,7 +1699,7 @@
       <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="44" t="n">
         <v>77.72</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1716,7 +1739,7 @@
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="44" t="n">
         <v>77.7</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1756,7 +1779,7 @@
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="44" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1796,7 +1819,7 @@
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="44" t="n">
         <v>77.83</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1836,7 +1859,7 @@
       <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="44" t="n">
         <v>77.7</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1876,7 +1899,7 @@
       <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="44" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1916,7 +1939,7 @@
       <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="44" t="n">
         <v>77.83</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1956,7 +1979,7 @@
       <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="44" t="n">
         <v>77.81</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -1996,7 +2019,7 @@
       <c r="C29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2036,7 +2059,7 @@
       <c r="C30" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="44" t="n">
         <v>77.84999999999999</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2076,7 +2099,7 @@
       <c r="C31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="44" t="n">
         <v>77.67</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2116,7 +2139,7 @@
       <c r="C32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="44" t="n">
         <v>77.83</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2156,7 +2179,7 @@
       <c r="C33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2196,7 +2219,7 @@
       <c r="C34" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="44" t="n">
         <v>77.72</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2236,7 +2259,7 @@
       <c r="C35" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="44" t="n">
         <v>77.83</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2276,7 +2299,7 @@
       <c r="C36" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="44" t="n">
         <v>77.7</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2316,7 +2339,7 @@
       <c r="C37" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="44" t="n">
         <v>77.81</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2356,7 +2379,7 @@
       <c r="C38" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="44" t="n">
         <v>77.81999999999999</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2396,7 +2419,7 @@
       <c r="C39" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2436,7 +2459,7 @@
       <c r="C40" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="44" t="n">
         <v>77.84</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2476,7 +2499,7 @@
       <c r="C41" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="44" t="n">
         <v>77.83</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2516,7 +2539,7 @@
       <c r="C42" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="44" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2556,7 +2579,7 @@
       <c r="C43" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="44" t="n">
         <v>77.7</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2596,7 +2619,7 @@
       <c r="C44" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="44" t="n">
         <v>77.88</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2636,7 +2659,7 @@
       <c r="C45" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="44" t="n">
         <v>77.86</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2676,7 +2699,7 @@
       <c r="C46" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="44" t="n">
         <v>77.84</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2716,7 +2739,7 @@
       <c r="C47" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="44" t="n">
         <v>77.81</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2756,7 +2779,7 @@
       <c r="C48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="44" t="n">
         <v>2.99</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2796,7 +2819,7 @@
       <c r="C49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="44" t="n">
         <v>8.68</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2837,7 +2860,7 @@
         <f>SUM(C4:C49)</f>
         <v/>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="45">
         <f>SUM(D4:D49)</f>
         <v/>
       </c>
@@ -2846,7 +2869,7 @@
         <v/>
       </c>
       <c r="F50" s="23">
-        <f>SUM(F4:F49)</f>
+        <f>SUMIF(E4:E49,"&gt;0",F4:F49)</f>
         <v/>
       </c>
       <c r="G50" s="24">
@@ -2881,7 +2904,7 @@
         <f>C50</f>
         <v/>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="46">
         <f>D50</f>
         <v/>
       </c>
@@ -2957,7 +2980,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -2965,7 +2987,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -6967,7 +6988,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -9152,7 +9172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -9167,7 +9187,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="39" t="inlineStr">
         <is>

--- a/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun29-Jun29.xlsx
+++ b/docs/reports/daily/NCR_Kavach_Unified_KPI_Jun29-Jun29.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3168,7 +3168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3246,6 +3246,11 @@
           <t>Valid Trip?</t>
         </is>
       </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Travel</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3302,6 +3307,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3358,6 +3368,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3414,6 +3429,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -3470,6 +3490,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -3526,6 +3551,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -3582,6 +3612,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -3638,6 +3673,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -3694,6 +3734,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -3750,6 +3795,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -3806,6 +3856,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -3862,6 +3917,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -3918,6 +3978,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -3974,6 +4039,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4030,6 +4100,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4086,6 +4161,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4142,6 +4222,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -4198,6 +4283,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -4254,6 +4344,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -4310,6 +4405,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -4366,6 +4466,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -4422,6 +4527,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -4478,6 +4588,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -4534,6 +4649,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -4590,6 +4710,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -4646,6 +4771,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4702,6 +4832,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -4758,6 +4893,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4814,6 +4954,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -4870,6 +5015,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -4926,6 +5076,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -4982,6 +5137,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -5038,6 +5198,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -5094,6 +5259,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -5150,6 +5320,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -5206,6 +5381,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -5262,6 +5442,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -5318,6 +5503,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -5374,6 +5564,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -5430,6 +5625,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -5486,6 +5686,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -5542,6 +5747,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -5598,6 +5808,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -5654,6 +5869,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -5710,6 +5930,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -5766,6 +5991,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -5822,6 +6052,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -5878,6 +6113,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -5934,6 +6174,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -5990,6 +6235,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -6046,6 +6296,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -6102,6 +6357,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -6158,6 +6418,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -6214,6 +6479,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -6270,6 +6540,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -6326,6 +6601,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -6382,6 +6662,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -6438,6 +6723,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -6494,6 +6784,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -6550,6 +6845,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -6606,6 +6906,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -6662,6 +6967,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -6718,6 +7028,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -6774,6 +7089,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -6830,6 +7150,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -6886,6 +7211,11 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -6940,6 +7270,11 @@
       <c r="L71" s="16" t="inlineStr">
         <is>
           <t>Valid</t>
+        </is>
+      </c>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>LC563, LC562, LC561, LC559, LC557, LC556, LC555, LC553, LC551, LC545, Chhata, LC540, Ajhai, LC535, Vrindavan Road, BCH</t>
         </is>
       </c>
     </row>
